--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_risk_info_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_risk_info_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>项目编号</t>
   </si>
@@ -556,139 +556,157 @@
     <t>林小明</t>
   </si>
   <si>
+    <t>PJ-2025-008</t>
+  </si>
+  <si>
+    <t>2025年4月30日</t>
+  </si>
+  <si>
+    <t>2025年4月8日</t>
+  </si>
+  <si>
+    <t>王鹏</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>李雪</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>周强</t>
+  </si>
+  <si>
     <t>PJ-2025-005</t>
   </si>
   <si>
+    <t>2025-2-1</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025-3-25</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>2025年07月31日</t>
+  </si>
+  <si>
+    <t>2025-13-25</t>
+  </si>
+  <si>
+    <t>2025/04/30</t>
+  </si>
+  <si>
+    <t>2025-13-08</t>
+  </si>
+  <si>
+    <t>黄磊</t>
+  </si>
+  <si>
+    <t>2025年4月10日</t>
+  </si>
+  <si>
+    <t>2025年02月01日</t>
+  </si>
+  <si>
+    <t>2025-13-10</t>
+  </si>
+  <si>
+    <t>秦川</t>
+  </si>
+  <si>
+    <t>2025年2月25日</t>
+  </si>
+  <si>
+    <t>20250/04/10</t>
+  </si>
+  <si>
+    <t>钱海</t>
+  </si>
+  <si>
+    <t>2025.1.10</t>
+  </si>
+  <si>
+    <t>2025.3.1</t>
+  </si>
+  <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>20205/03/25</t>
+  </si>
+  <si>
+    <t>2025-2-25</t>
+  </si>
+  <si>
+    <t>20250/03/20</t>
+  </si>
+  <si>
+    <t>2025-03-32</t>
+  </si>
+  <si>
+    <t>2025年04月30日</t>
+  </si>
+  <si>
+    <t>2025/3/1</t>
+  </si>
+  <si>
+    <t>2025-04</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>2025/1/25</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>2025/2/15</t>
+  </si>
+  <si>
+    <t>2025.3.25</t>
+  </si>
+  <si>
+    <t>2025.4.10</t>
+  </si>
+  <si>
+    <t>20250/03/25</t>
+  </si>
+  <si>
     <t>未知</t>
   </si>
   <si>
+    <t>2025.3.31</t>
+  </si>
+  <si>
+    <t>2025.3.20</t>
+  </si>
+  <si>
     <t>赵敏</t>
   </si>
   <si>
-    <t>2025年03月01日</t>
-  </si>
-  <si>
-    <t>PJ-2025-008</t>
-  </si>
-  <si>
-    <t>2025-04</t>
-  </si>
-  <si>
-    <t>郭伟</t>
-  </si>
-  <si>
-    <t>PJ-2025-004</t>
-  </si>
-  <si>
-    <t>2025-02</t>
-  </si>
-  <si>
-    <t>2025-13-10</t>
-  </si>
-  <si>
-    <t>钱海</t>
-  </si>
-  <si>
-    <t>20250/04/10</t>
-  </si>
-  <si>
-    <t>PJ-2025-006</t>
-  </si>
-  <si>
-    <t>2025年3月15日</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>秦川</t>
-  </si>
-  <si>
-    <t>周强</t>
-  </si>
-  <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>2025.4.10</t>
-  </si>
-  <si>
-    <t>王鹏</t>
+    <t>2025-4-10</t>
   </si>
   <si>
     <t>2025/04/10</t>
   </si>
   <si>
-    <t>2025/3/1</t>
-  </si>
-  <si>
-    <t>李雪</t>
-  </si>
-  <si>
-    <t>20205/09/30</t>
-  </si>
-  <si>
     <t>20205/03/31</t>
   </si>
   <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>20205/06/30</t>
-  </si>
-  <si>
-    <t>2025-4-10</t>
-  </si>
-  <si>
-    <t>2025/4/10</t>
-  </si>
-  <si>
-    <t>20205/01/10</t>
-  </si>
-  <si>
-    <t>2025-03-32</t>
-  </si>
-  <si>
-    <t>20250/01/15</t>
-  </si>
-  <si>
-    <t>2025年4月1日</t>
-  </si>
-  <si>
-    <t>2025-7-31</t>
-  </si>
-  <si>
-    <t>20250/01/20</t>
-  </si>
-  <si>
-    <t>2025-1-10</t>
-  </si>
-  <si>
-    <t>20205/04/10</t>
-  </si>
-  <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>2025-04-32</t>
-  </si>
-  <si>
-    <t>2025年2月15日</t>
-  </si>
-  <si>
-    <t>2025-13-25</t>
-  </si>
-  <si>
-    <t>2025年1月25日</t>
-  </si>
-  <si>
-    <t>2025-13-20</t>
+    <t>2025年02月28日</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1797,7 @@
         <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="N12" t="s">
         <v>44</v>
@@ -1797,7 +1815,7 @@
         <v>48</v>
       </c>
       <c r="S12" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="T12" t="s">
         <v>50</v>
@@ -1818,7 +1836,7 @@
         <v>55</v>
       </c>
       <c r="Z12" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="AA12" t="s">
         <v>50</v>
@@ -1833,12 +1851,12 @@
         <v>50</v>
       </c>
       <c r="AE12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -1853,7 +1871,7 @@
         <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
         <v>63</v>
@@ -1928,12 +1946,12 @@
         <v>50</v>
       </c>
       <c r="AE13" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
@@ -1987,7 +2005,7 @@
         <v>92</v>
       </c>
       <c r="S14" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="T14" t="s">
         <v>50</v>
@@ -2023,12 +2041,12 @@
         <v>50</v>
       </c>
       <c r="AE14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
         <v>98</v>
@@ -2043,7 +2061,7 @@
         <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
         <v>103</v>
@@ -2064,7 +2082,7 @@
         <v>106</v>
       </c>
       <c r="M15" t="s">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s">
         <v>108</v>
@@ -2103,7 +2121,7 @@
         <v>55</v>
       </c>
       <c r="Z15" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s">
         <v>108</v>
@@ -2118,12 +2136,12 @@
         <v>108</v>
       </c>
       <c r="AE15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
         <v>116</v>
@@ -2177,7 +2195,7 @@
         <v>37</v>
       </c>
       <c r="S16" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="T16" t="s">
         <v>50</v>
@@ -2207,18 +2225,18 @@
         <v>128</v>
       </c>
       <c r="AC16" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="AD16" t="s">
         <v>50</v>
       </c>
       <c r="AE16" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>129</v>
@@ -2308,12 +2326,12 @@
         <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s">
         <v>138</v>
@@ -2349,7 +2367,7 @@
         <v>146</v>
       </c>
       <c r="M18" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s">
         <v>148</v>
@@ -2367,7 +2385,7 @@
         <v>110</v>
       </c>
       <c r="S18" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="T18" t="s">
         <v>50</v>
@@ -2403,12 +2421,12 @@
         <v>50</v>
       </c>
       <c r="AE18" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
         <v>155</v>
@@ -2462,7 +2480,7 @@
         <v>110</v>
       </c>
       <c r="S19" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="T19" t="s">
         <v>164</v>
@@ -2498,12 +2516,12 @@
         <v>164</v>
       </c>
       <c r="AE19" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>166</v>
@@ -2518,7 +2536,7 @@
         <v>167</v>
       </c>
       <c r="F20" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="G20" t="s">
         <v>169</v>
@@ -2593,12 +2611,12 @@
         <v>50</v>
       </c>
       <c r="AE20" t="s">
-        <v>192</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
         <v>175</v>
@@ -2688,12 +2706,12 @@
         <v>120</v>
       </c>
       <c r="AE21" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
@@ -2729,7 +2747,7 @@
         <v>42</v>
       </c>
       <c r="M22" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="N22" t="s">
         <v>44</v>
@@ -2747,7 +2765,7 @@
         <v>48</v>
       </c>
       <c r="S22" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="T22" t="s">
         <v>50</v>
@@ -2768,7 +2786,7 @@
         <v>55</v>
       </c>
       <c r="Z22" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="AA22" t="s">
         <v>50</v>
@@ -2783,12 +2801,12 @@
         <v>50</v>
       </c>
       <c r="AE22" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
@@ -2878,12 +2896,12 @@
         <v>50</v>
       </c>
       <c r="AE23" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
@@ -2937,7 +2955,7 @@
         <v>92</v>
       </c>
       <c r="S24" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="T24" t="s">
         <v>50</v>
@@ -2973,12 +2991,12 @@
         <v>50</v>
       </c>
       <c r="AE24" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>98</v>
@@ -2993,7 +3011,7 @@
         <v>101</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="G25" t="s">
         <v>103</v>
@@ -3068,7 +3086,7 @@
         <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -3127,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="S26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="T26" t="s">
         <v>50</v>
@@ -3163,7 +3181,7 @@
         <v>50</v>
       </c>
       <c r="AE26" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27">
@@ -3222,7 +3240,7 @@
         <v>37</v>
       </c>
       <c r="S27" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="T27" t="s">
         <v>108</v>
@@ -3258,12 +3276,12 @@
         <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
         <v>138</v>
@@ -3347,18 +3365,18 @@
         <v>76</v>
       </c>
       <c r="AC28" t="s">
-        <v>202</v>
+        <v>49</v>
       </c>
       <c r="AD28" t="s">
         <v>50</v>
       </c>
       <c r="AE28" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>155</v>
@@ -3394,7 +3412,7 @@
         <v>161</v>
       </c>
       <c r="M29" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s">
         <v>63</v>
@@ -3433,7 +3451,7 @@
         <v>55</v>
       </c>
       <c r="Z29" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="AA29" t="s">
         <v>164</v>
@@ -3442,13 +3460,13 @@
         <v>76</v>
       </c>
       <c r="AC29" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
       <c r="AD29" t="s">
         <v>164</v>
       </c>
       <c r="AE29" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
@@ -3537,18 +3555,18 @@
         <v>76</v>
       </c>
       <c r="AC30" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="AD30" t="s">
         <v>50</v>
       </c>
       <c r="AE30" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s">
         <v>175</v>
@@ -3658,7 +3676,7 @@
         <v>35</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="G32" t="s">
         <v>37</v>
@@ -3697,7 +3715,7 @@
         <v>48</v>
       </c>
       <c r="S32" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="T32" t="s">
         <v>50</v>
@@ -3727,18 +3745,18 @@
         <v>57</v>
       </c>
       <c r="AC32" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="AD32" t="s">
         <v>50</v>
       </c>
       <c r="AE32" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -3753,7 +3771,7 @@
         <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G33" t="s">
         <v>63</v>
@@ -3774,7 +3792,7 @@
         <v>66</v>
       </c>
       <c r="M33" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="N33" t="s">
         <v>68</v>
@@ -3828,12 +3846,12 @@
         <v>50</v>
       </c>
       <c r="AE33" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
         <v>78</v>
@@ -3848,7 +3866,7 @@
         <v>81</v>
       </c>
       <c r="F34" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s">
         <v>83</v>
@@ -3869,7 +3887,7 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="N34" t="s">
         <v>88</v>
@@ -3923,12 +3941,12 @@
         <v>50</v>
       </c>
       <c r="AE34" t="s">
-        <v>188</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
         <v>98</v>
@@ -3964,7 +3982,7 @@
         <v>106</v>
       </c>
       <c r="M35" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="N35" t="s">
         <v>108</v>
@@ -4018,12 +4036,12 @@
         <v>108</v>
       </c>
       <c r="AE35" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s">
         <v>116</v>
@@ -4113,12 +4131,12 @@
         <v>50</v>
       </c>
       <c r="AE36" t="s">
-        <v>113</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>194</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>129</v>
@@ -4202,18 +4220,18 @@
         <v>137</v>
       </c>
       <c r="AC37" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="AD37" t="s">
         <v>108</v>
       </c>
       <c r="AE37" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
         <v>138</v>
@@ -4228,7 +4246,7 @@
         <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="G38" t="s">
         <v>143</v>
@@ -4267,7 +4285,7 @@
         <v>110</v>
       </c>
       <c r="S38" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="T38" t="s">
         <v>50</v>
@@ -4303,12 +4321,12 @@
         <v>50</v>
       </c>
       <c r="AE38" t="s">
-        <v>200</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
         <v>155</v>
@@ -4383,7 +4401,7 @@
         <v>55</v>
       </c>
       <c r="Z39" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="AA39" t="s">
         <v>164</v>
@@ -4398,12 +4416,12 @@
         <v>164</v>
       </c>
       <c r="AE39" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s">
         <v>166</v>
@@ -4493,12 +4511,12 @@
         <v>50</v>
       </c>
       <c r="AE40" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s">
         <v>175</v>
@@ -4534,7 +4552,7 @@
         <v>179</v>
       </c>
       <c r="M41" t="s">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="N41" t="s">
         <v>108</v>
@@ -4552,7 +4570,7 @@
         <v>110</v>
       </c>
       <c r="S41" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="T41" t="s">
         <v>120</v>
@@ -4582,18 +4600,18 @@
         <v>76</v>
       </c>
       <c r="AC41" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="AD41" t="s">
         <v>120</v>
       </c>
       <c r="AE41" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
         <v>32</v>
@@ -4629,7 +4647,7 @@
         <v>42</v>
       </c>
       <c r="M42" t="s">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s">
         <v>44</v>
@@ -4677,18 +4695,18 @@
         <v>57</v>
       </c>
       <c r="AC42" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="AD42" t="s">
         <v>50</v>
       </c>
       <c r="AE42" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -4703,7 +4721,7 @@
         <v>61</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="G43" t="s">
         <v>63</v>
@@ -4724,7 +4742,7 @@
         <v>66</v>
       </c>
       <c r="M43" t="s">
-        <v>210</v>
+        <v>67</v>
       </c>
       <c r="N43" t="s">
         <v>68</v>
@@ -4778,12 +4796,12 @@
         <v>50</v>
       </c>
       <c r="AE43" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
@@ -4837,7 +4855,7 @@
         <v>92</v>
       </c>
       <c r="S44" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="T44" t="s">
         <v>50</v>
@@ -4873,12 +4891,12 @@
         <v>50</v>
       </c>
       <c r="AE44" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
         <v>98</v>
@@ -4968,12 +4986,12 @@
         <v>108</v>
       </c>
       <c r="AE45" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
         <v>116</v>
@@ -5057,18 +5075,18 @@
         <v>128</v>
       </c>
       <c r="AC46" t="s">
-        <v>211</v>
+        <v>49</v>
       </c>
       <c r="AD46" t="s">
         <v>50</v>
       </c>
       <c r="AE46" t="s">
-        <v>181</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
         <v>129</v>
@@ -5152,18 +5170,18 @@
         <v>137</v>
       </c>
       <c r="AC47" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="AD47" t="s">
         <v>108</v>
       </c>
       <c r="AE47" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s">
         <v>138</v>
@@ -5199,7 +5217,7 @@
         <v>146</v>
       </c>
       <c r="M48" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="N48" t="s">
         <v>148</v>
@@ -5247,18 +5265,18 @@
         <v>76</v>
       </c>
       <c r="AC48" t="s">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="AD48" t="s">
         <v>50</v>
       </c>
       <c r="AE48" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="B49" t="s">
         <v>155</v>
@@ -5348,12 +5366,12 @@
         <v>164</v>
       </c>
       <c r="AE49" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B50" t="s">
         <v>166</v>
@@ -5443,12 +5461,12 @@
         <v>50</v>
       </c>
       <c r="AE50" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B51" t="s">
         <v>175</v>
@@ -5463,7 +5481,7 @@
         <v>177</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="G51" t="s">
         <v>92</v>
@@ -5538,12 +5556,12 @@
         <v>120</v>
       </c>
       <c r="AE51" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
         <v>32</v>
@@ -5558,7 +5576,7 @@
         <v>35</v>
       </c>
       <c r="F52" t="s">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="G52" t="s">
         <v>37</v>
@@ -5618,7 +5636,7 @@
         <v>55</v>
       </c>
       <c r="Z52" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="AA52" t="s">
         <v>50</v>
@@ -5633,7 +5651,7 @@
         <v>50</v>
       </c>
       <c r="AE52" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53">
@@ -5728,12 +5746,12 @@
         <v>50</v>
       </c>
       <c r="AE53" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
         <v>78</v>
@@ -5748,7 +5766,7 @@
         <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="G54" t="s">
         <v>83</v>
@@ -5787,7 +5805,7 @@
         <v>92</v>
       </c>
       <c r="S54" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="T54" t="s">
         <v>50</v>
@@ -5823,12 +5841,12 @@
         <v>50</v>
       </c>
       <c r="AE54" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
         <v>98</v>
@@ -5882,7 +5900,7 @@
         <v>110</v>
       </c>
       <c r="S55" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="T55" t="s">
         <v>108</v>
@@ -5912,18 +5930,18 @@
         <v>76</v>
       </c>
       <c r="AC55" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="AD55" t="s">
         <v>108</v>
       </c>
       <c r="AE55" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
         <v>116</v>
@@ -5977,7 +5995,7 @@
         <v>37</v>
       </c>
       <c r="S56" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="T56" t="s">
         <v>50</v>
@@ -6013,12 +6031,12 @@
         <v>50</v>
       </c>
       <c r="AE56" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
         <v>129</v>
@@ -6033,7 +6051,7 @@
         <v>131</v>
       </c>
       <c r="F57" t="s">
-        <v>215</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s">
         <v>48</v>
@@ -6102,18 +6120,18 @@
         <v>137</v>
       </c>
       <c r="AC57" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="AD57" t="s">
         <v>108</v>
       </c>
       <c r="AE57" t="s">
-        <v>72</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -6128,7 +6146,7 @@
         <v>141</v>
       </c>
       <c r="F58" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="G58" t="s">
         <v>143</v>
@@ -6149,7 +6167,7 @@
         <v>146</v>
       </c>
       <c r="M58" t="s">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="N58" t="s">
         <v>148</v>
@@ -6203,12 +6221,12 @@
         <v>50</v>
       </c>
       <c r="AE58" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
         <v>155</v>
@@ -6223,7 +6241,7 @@
         <v>157</v>
       </c>
       <c r="F59" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="G59" t="s">
         <v>48</v>
@@ -6292,18 +6310,18 @@
         <v>76</v>
       </c>
       <c r="AC59" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="AD59" t="s">
         <v>164</v>
       </c>
       <c r="AE59" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
         <v>166</v>
@@ -6318,7 +6336,7 @@
         <v>167</v>
       </c>
       <c r="F60" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="G60" t="s">
         <v>169</v>
@@ -6339,7 +6357,7 @@
         <v>171</v>
       </c>
       <c r="M60" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="N60" t="s">
         <v>124</v>
@@ -6393,12 +6411,12 @@
         <v>50</v>
       </c>
       <c r="AE60" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B61" t="s">
         <v>175</v>
@@ -6434,7 +6452,7 @@
         <v>179</v>
       </c>
       <c r="M61" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="N61" t="s">
         <v>108</v>
@@ -6452,7 +6470,7 @@
         <v>110</v>
       </c>
       <c r="S61" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="T61" t="s">
         <v>120</v>
@@ -6482,18 +6500,18 @@
         <v>76</v>
       </c>
       <c r="AC61" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="AD61" t="s">
         <v>120</v>
       </c>
       <c r="AE61" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
@@ -6508,7 +6526,7 @@
         <v>35</v>
       </c>
       <c r="F62" t="s">
-        <v>219</v>
+        <v>36</v>
       </c>
       <c r="G62" t="s">
         <v>37</v>
@@ -6547,7 +6565,7 @@
         <v>48</v>
       </c>
       <c r="S62" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="T62" t="s">
         <v>50</v>
@@ -6583,12 +6601,12 @@
         <v>50</v>
       </c>
       <c r="AE62" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B63" t="s">
         <v>58</v>
@@ -6642,7 +6660,7 @@
         <v>37</v>
       </c>
       <c r="S63" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="T63" t="s">
         <v>50</v>
@@ -6678,12 +6696,12 @@
         <v>50</v>
       </c>
       <c r="AE63" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>190</v>
       </c>
       <c r="B64" t="s">
         <v>78</v>
@@ -6773,7 +6791,7 @@
         <v>50</v>
       </c>
       <c r="AE64" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65">
@@ -6868,12 +6886,12 @@
         <v>108</v>
       </c>
       <c r="AE65" t="s">
-        <v>206</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
         <v>116</v>
@@ -6963,12 +6981,12 @@
         <v>50</v>
       </c>
       <c r="AE66" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
         <v>129</v>
@@ -6983,7 +7001,7 @@
         <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="G67" t="s">
         <v>48</v>
@@ -7058,12 +7076,12 @@
         <v>108</v>
       </c>
       <c r="AE67" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
         <v>138</v>
@@ -7147,18 +7165,18 @@
         <v>76</v>
       </c>
       <c r="AC68" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD68" t="s">
         <v>50</v>
       </c>
       <c r="AE68" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="B69" t="s">
         <v>155</v>
@@ -7173,7 +7191,7 @@
         <v>157</v>
       </c>
       <c r="F69" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="G69" t="s">
         <v>48</v>
@@ -7248,12 +7266,12 @@
         <v>164</v>
       </c>
       <c r="AE69" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
         <v>166</v>
@@ -7337,18 +7355,18 @@
         <v>76</v>
       </c>
       <c r="AC70" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD70" t="s">
         <v>50</v>
       </c>
       <c r="AE70" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B71" t="s">
         <v>175</v>
@@ -7402,7 +7420,7 @@
         <v>110</v>
       </c>
       <c r="S71" t="s">
-        <v>119</v>
+        <v>192</v>
       </c>
       <c r="T71" t="s">
         <v>120</v>
@@ -7438,12 +7456,12 @@
         <v>120</v>
       </c>
       <c r="AE71" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s">
         <v>32</v>
@@ -7518,7 +7536,7 @@
         <v>55</v>
       </c>
       <c r="Z72" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="AA72" t="s">
         <v>50</v>
@@ -7527,18 +7545,18 @@
         <v>57</v>
       </c>
       <c r="AC72" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="AD72" t="s">
         <v>50</v>
       </c>
       <c r="AE72" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
         <v>58</v>
@@ -7622,18 +7640,18 @@
         <v>76</v>
       </c>
       <c r="AC73" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AD73" t="s">
         <v>50</v>
       </c>
       <c r="AE73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
         <v>78</v>
@@ -7648,7 +7666,7 @@
         <v>81</v>
       </c>
       <c r="F74" t="s">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="G74" t="s">
         <v>83</v>
@@ -7723,12 +7741,12 @@
         <v>50</v>
       </c>
       <c r="AE74" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B75" t="s">
         <v>98</v>
@@ -7803,7 +7821,7 @@
         <v>55</v>
       </c>
       <c r="Z75" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="AA75" t="s">
         <v>108</v>
@@ -7818,12 +7836,12 @@
         <v>108</v>
       </c>
       <c r="AE75" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B76" t="s">
         <v>116</v>
@@ -7913,12 +7931,12 @@
         <v>50</v>
       </c>
       <c r="AE76" t="s">
-        <v>184</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B77" t="s">
         <v>129</v>
@@ -7954,7 +7972,7 @@
         <v>133</v>
       </c>
       <c r="M77" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="N77" t="s">
         <v>108</v>
@@ -8008,12 +8026,12 @@
         <v>108</v>
       </c>
       <c r="AE77" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -8067,7 +8085,7 @@
         <v>110</v>
       </c>
       <c r="S78" t="s">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="T78" t="s">
         <v>50</v>
@@ -8097,18 +8115,18 @@
         <v>76</v>
       </c>
       <c r="AC78" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="AD78" t="s">
         <v>50</v>
       </c>
       <c r="AE78" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B79" t="s">
         <v>155</v>
@@ -8144,7 +8162,7 @@
         <v>161</v>
       </c>
       <c r="M79" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="N79" t="s">
         <v>63</v>
@@ -8162,7 +8180,7 @@
         <v>110</v>
       </c>
       <c r="S79" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="T79" t="s">
         <v>164</v>
@@ -8183,7 +8201,7 @@
         <v>55</v>
       </c>
       <c r="Z79" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="AA79" t="s">
         <v>164</v>
@@ -8198,12 +8216,12 @@
         <v>164</v>
       </c>
       <c r="AE79" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B80" t="s">
         <v>166</v>
@@ -8287,18 +8305,18 @@
         <v>76</v>
       </c>
       <c r="AC80" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="AD80" t="s">
         <v>50</v>
       </c>
       <c r="AE80" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B81" t="s">
         <v>175</v>
@@ -8313,7 +8331,7 @@
         <v>177</v>
       </c>
       <c r="F81" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="G81" t="s">
         <v>92</v>
@@ -8352,7 +8370,7 @@
         <v>110</v>
       </c>
       <c r="S81" t="s">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="T81" t="s">
         <v>120</v>
@@ -8388,7 +8406,7 @@
         <v>120</v>
       </c>
       <c r="AE81" t="s">
-        <v>200</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
